--- a/utils/Tools/excel/11_bag_背包.xlsx
+++ b/utils/Tools/excel/11_bag_背包.xlsx
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
   <si>
     <t>道具id</t>
   </si>
@@ -149,10 +149,7 @@
     <t>[]{int id;int num}</t>
   </si>
   <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>c</t>
+    <t>cs</t>
   </si>
   <si>
     <t>金币</t>
@@ -1481,7 +1478,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>19</v>
@@ -1507,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
@@ -1529,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -1551,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
@@ -1573,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
@@ -1595,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
@@ -1617,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
@@ -1641,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -1656,7 +1653,7 @@
         <v>10</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1667,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
@@ -1682,7 +1679,7 @@
         <v>1000</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1693,7 +1690,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" s="2">
         <v>3</v>
@@ -1717,7 +1714,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2">
         <v>3</v>
@@ -1741,7 +1738,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" s="2">
         <v>3</v>
@@ -1765,7 +1762,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -1789,7 +1786,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -1813,7 +1810,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" s="2">
         <v>2</v>
@@ -1837,7 +1834,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" s="2">
         <v>2</v>
@@ -1861,7 +1858,7 @@
         <v>4</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
@@ -1885,7 +1882,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" s="2">
         <v>2</v>
@@ -1909,7 +1906,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D22" s="2">
         <v>4</v>
@@ -1924,7 +1921,7 @@
         <v>1000</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
